--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:49</t>
+    <t xml:space="preserve">2026-09-09 20:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:13</t>
+    <t xml:space="preserve">2026-09-18 17:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_los_lagos.xlsx
@@ -30,96 +30,96 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Palena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puyehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pablo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frutillar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Varas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Juan de la Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maullín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochamó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futaleufú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queilén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llanquihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Octay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quellón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Muermos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chonchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calbuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puqueldón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Montt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Montt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puqueldón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osorno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purranque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calbuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chonchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Muermos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quellón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Octay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llanquihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queilén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalcahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Castro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futaleufú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochamó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maullín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Juan de la Costa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Varas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frutillar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Negro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualaihué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pablo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puyehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palena</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:06</t>
+    <t xml:space="preserve">2026-09-27 21:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -549,13 +549,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5003</v>
+        <v>2584</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5061</v>
+        <v>1824</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>98.85</v>
+        <v>141.67</v>
       </c>
     </row>
     <row r="3">
@@ -563,13 +563,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4107</v>
+        <v>14950</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4120</v>
+        <v>11813</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>99.68</v>
+        <v>126.56</v>
       </c>
     </row>
     <row r="4">
@@ -577,13 +577,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>277529</v>
+        <v>13230</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>278255</v>
+        <v>10543</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>99.74</v>
+        <v>125.49</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4218</v>
+        <v>11679</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4191</v>
+        <v>9579</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>100.64</v>
+        <v>121.92</v>
       </c>
     </row>
     <row r="6">
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>177391</v>
+        <v>16678</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>175670</v>
+        <v>14133</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>100.98</v>
+        <v>118.01</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +619,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>21460</v>
+        <v>24048</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>20998</v>
+        <v>20678</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>102.2</v>
+        <v>116.3</v>
       </c>
     </row>
     <row r="8">
@@ -633,13 +633,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>38680</v>
+        <v>58852</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>37429</v>
+        <v>50669</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>103.34</v>
+        <v>116.15</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         <v>8539</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>8212</v>
+        <v>7482</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>103.98</v>
+        <v>114.13</v>
       </c>
     </row>
     <row r="10">
@@ -661,13 +661,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9222</v>
+        <v>47899</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8760</v>
+        <v>42516</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>105.27</v>
+        <v>112.66</v>
       </c>
     </row>
     <row r="11">
@@ -675,13 +675,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>17341</v>
+        <v>16606</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>16213</v>
+        <v>14775</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>106.96</v>
+        <v>112.39</v>
       </c>
     </row>
     <row r="12">
@@ -689,13 +689,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>19074</v>
+        <v>4446</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>17831</v>
+        <v>3960</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>106.97</v>
+        <v>112.27</v>
       </c>
     </row>
     <row r="13">
@@ -703,13 +703,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>32171</v>
+        <v>3241</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>29942</v>
+        <v>2889</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>107.44</v>
+        <v>112.18</v>
       </c>
     </row>
     <row r="14">
@@ -717,13 +717,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>13605</v>
+        <v>54181</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>12593</v>
+        <v>48482</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>108.04</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="15">
@@ -731,13 +731,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>9892</v>
+        <v>17132</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>9089</v>
+        <v>15368</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>108.83</v>
+        <v>111.48</v>
       </c>
     </row>
     <row r="16">
@@ -745,13 +745,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>20551</v>
+        <v>6080</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>18811</v>
+        <v>5543</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>109.25</v>
+        <v>109.69</v>
       </c>
     </row>
     <row r="17">
@@ -759,13 +759,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>6080</v>
+        <v>20551</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5543</v>
+        <v>18811</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>109.69</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="18">
@@ -773,13 +773,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>17132</v>
+        <v>9892</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>15368</v>
+        <v>9089</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>111.48</v>
+        <v>108.83</v>
       </c>
     </row>
     <row r="19">
@@ -787,13 +787,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>54181</v>
+        <v>13605</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>48482</v>
+        <v>12593</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>111.75</v>
+        <v>108.04</v>
       </c>
     </row>
     <row r="20">
@@ -801,13 +801,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3241</v>
+        <v>32171</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2889</v>
+        <v>29942</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>112.18</v>
+        <v>107.44</v>
       </c>
     </row>
     <row r="21">
@@ -815,13 +815,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4446</v>
+        <v>19074</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3960</v>
+        <v>17831</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>112.27</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="22">
@@ -829,13 +829,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>16606</v>
+        <v>17341</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>14775</v>
+        <v>16213</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>112.39</v>
+        <v>106.96</v>
       </c>
     </row>
     <row r="23">
@@ -843,13 +843,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>47899</v>
+        <v>9222</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>42516</v>
+        <v>8760</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>112.66</v>
+        <v>105.27</v>
       </c>
     </row>
     <row r="24">
@@ -860,10 +860,10 @@
         <v>8539</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>7482</v>
+        <v>8212</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>114.13</v>
+        <v>103.98</v>
       </c>
     </row>
     <row r="25">
@@ -871,13 +871,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>58852</v>
+        <v>38680</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>50669</v>
+        <v>37429</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>116.15</v>
+        <v>103.34</v>
       </c>
     </row>
     <row r="26">
@@ -885,13 +885,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>24048</v>
+        <v>21460</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>20678</v>
+        <v>20998</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>116.3</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="27">
@@ -899,13 +899,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>16678</v>
+        <v>177391</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>14133</v>
+        <v>175670</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>118.01</v>
+        <v>100.98</v>
       </c>
     </row>
     <row r="28">
@@ -913,13 +913,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>11679</v>
+        <v>4218</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>9579</v>
+        <v>4191</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>121.92</v>
+        <v>100.64</v>
       </c>
     </row>
     <row r="29">
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>13230</v>
+        <v>277529</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>10543</v>
+        <v>278255</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>125.49</v>
+        <v>99.74</v>
       </c>
     </row>
     <row r="30">
@@ -941,13 +941,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>14950</v>
+        <v>4107</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>11813</v>
+        <v>4120</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>126.56</v>
+        <v>99.68</v>
       </c>
     </row>
     <row r="31">
@@ -955,13 +955,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2584</v>
+        <v>5003</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1824</v>
+        <v>5061</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>141.67</v>
+        <v>98.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_los_lagos.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:53</t>
+    <t xml:space="preserve">2026-10-05 05:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
